--- a/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=03/M10+_device03_10-13-2024 15:09:22.xlsx
+++ b/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=03/M10+_device03_10-13-2024 15:09:22.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Downloads/M10+_device03_10-13-2024 15:09:"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Developer/Personal/Trellis Air Quality/trellis-aq/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=03/M10+_device03_10-13-2024 15:09:"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE6BDDE-9494-0745-A860-8E3FFE9C55EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE07943-8AF0-D44F-87E6-549583E47FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="880" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="563">
   <si>
     <t>NO.</t>
   </si>
@@ -1333,12 +1333,6 @@
     <t>2024-10-13 14:00:00(+08:00)</t>
   </si>
   <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>2024-10-13 15:00:00(+08:00)</t>
-  </si>
-  <si>
     <t>AQI</t>
   </si>
   <si>
@@ -1631,9 +1625,6 @@
   </si>
   <si>
     <t>608</t>
-  </si>
-  <si>
-    <t>594</t>
   </si>
   <si>
     <t>TVOC</t>
@@ -2069,7 +2060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -2093,19 +2084,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2122,13 +2113,13 @@
         <v>185</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>168</v>
@@ -2148,13 +2139,13 @@
         <v>175</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>168</v>
@@ -2174,13 +2165,13 @@
         <v>165</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>179</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>168</v>
@@ -2200,13 +2191,13 @@
         <v>165</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>168</v>
@@ -2226,13 +2217,13 @@
         <v>163</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>75</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>168</v>
@@ -2252,13 +2243,13 @@
         <v>165</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>87</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>168</v>
@@ -2278,13 +2269,13 @@
         <v>165</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>94</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>170</v>
@@ -2304,13 +2295,13 @@
         <v>165</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>103</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>168</v>
@@ -2330,13 +2321,13 @@
         <v>165</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>103</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>170</v>
@@ -2356,13 +2347,13 @@
         <v>150</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>168</v>
@@ -2382,13 +2373,13 @@
         <v>142</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>170</v>
@@ -2408,13 +2399,13 @@
         <v>142</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>168</v>
@@ -2434,13 +2425,13 @@
         <v>115</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>168</v>
@@ -2460,13 +2451,13 @@
         <v>87</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>168</v>
@@ -2486,13 +2477,13 @@
         <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>168</v>
@@ -2512,13 +2503,13 @@
         <v>72</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>168</v>
@@ -2538,13 +2529,13 @@
         <v>87</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>168</v>
@@ -2564,13 +2555,13 @@
         <v>105</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>168</v>
@@ -2590,13 +2581,13 @@
         <v>194</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>168</v>
@@ -2616,13 +2607,13 @@
         <v>207</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>145</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>168</v>
@@ -2642,13 +2633,13 @@
         <v>204</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>165</v>
@@ -2668,13 +2659,13 @@
         <v>194</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>177</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>165</v>
@@ -2694,13 +2685,13 @@
         <v>213</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>371</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>165</v>
@@ -2720,13 +2711,13 @@
         <v>182</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>165</v>
@@ -2746,13 +2737,13 @@
         <v>170</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>182</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>165</v>
@@ -2772,13 +2763,13 @@
         <v>158</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>165</v>
@@ -2798,13 +2789,13 @@
         <v>150</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>163</v>
@@ -2824,13 +2815,13 @@
         <v>131</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>97</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>163</v>
@@ -2850,13 +2841,13 @@
         <v>128</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>100</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>165</v>
@@ -2876,13 +2867,13 @@
         <v>125</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>165</v>
@@ -2902,13 +2893,13 @@
         <v>125</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>168</v>
@@ -2928,13 +2919,13 @@
         <v>125</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>165</v>
@@ -2954,13 +2945,13 @@
         <v>118</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>165</v>
@@ -2980,13 +2971,13 @@
         <v>103</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>165</v>
@@ -3006,13 +2997,13 @@
         <v>103</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>165</v>
@@ -3032,13 +3023,13 @@
         <v>100</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>165</v>
@@ -3058,13 +3049,13 @@
         <v>103</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>165</v>
@@ -3084,13 +3075,13 @@
         <v>108</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>165</v>
@@ -3110,13 +3101,13 @@
         <v>105</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>165</v>
@@ -3136,13 +3127,13 @@
         <v>103</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>163</v>
@@ -3162,13 +3153,13 @@
         <v>97</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>165</v>
@@ -3188,13 +3179,13 @@
         <v>100</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>165</v>
@@ -3214,13 +3205,13 @@
         <v>103</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>165</v>
@@ -3240,13 +3231,13 @@
         <v>105</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>163</v>
@@ -3266,13 +3257,13 @@
         <v>161</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>163</v>
@@ -3292,13 +3283,13 @@
         <v>148</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>161</v>
@@ -3318,13 +3309,13 @@
         <v>139</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>179</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>161</v>
@@ -3344,13 +3335,13 @@
         <v>125</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>175</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>163</v>
@@ -3370,13 +3361,13 @@
         <v>112</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>266</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>163</v>
@@ -3396,13 +3387,13 @@
         <v>112</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>302</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>161</v>
@@ -3422,13 +3413,13 @@
         <v>110</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>161</v>
@@ -3448,13 +3439,13 @@
         <v>120</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>161</v>
@@ -3474,13 +3465,13 @@
         <v>110</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>161</v>
@@ -3500,13 +3491,13 @@
         <v>108</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>161</v>
@@ -3526,13 +3517,13 @@
         <v>145</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>163</v>
@@ -3552,13 +3543,13 @@
         <v>165</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>163</v>
@@ -3578,13 +3569,13 @@
         <v>155</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>163</v>
@@ -3604,13 +3595,13 @@
         <v>155</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>163</v>
@@ -3630,13 +3621,13 @@
         <v>155</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>163</v>
@@ -3656,13 +3647,13 @@
         <v>155</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>163</v>
@@ -3682,13 +3673,13 @@
         <v>155</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>163</v>
@@ -3708,13 +3699,13 @@
         <v>150</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>163</v>
@@ -3734,13 +3725,13 @@
         <v>150</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>161</v>
@@ -3760,13 +3751,13 @@
         <v>148</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>161</v>
@@ -3786,13 +3777,13 @@
         <v>150</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>161</v>
@@ -3812,13 +3803,13 @@
         <v>155</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>161</v>
@@ -3838,13 +3829,13 @@
         <v>163</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>161</v>
@@ -3864,13 +3855,13 @@
         <v>168</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>142</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>161</v>
@@ -3890,13 +3881,13 @@
         <v>163</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>145</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>158</v>
@@ -3916,13 +3907,13 @@
         <v>158</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>148</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>158</v>
@@ -3942,13 +3933,13 @@
         <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>158</v>
@@ -3968,13 +3959,13 @@
         <v>153</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>175</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>158</v>
@@ -3994,13 +3985,13 @@
         <v>150</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>155</v>
@@ -4020,13 +4011,13 @@
         <v>148</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>278</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>158</v>
@@ -4046,13 +4037,13 @@
         <v>219</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>337</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>158</v>
@@ -4072,13 +4063,13 @@
         <v>182</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>158</v>
@@ -4098,13 +4089,13 @@
         <v>177</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>103</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>158</v>
@@ -4124,13 +4115,13 @@
         <v>179</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>161</v>
@@ -4150,13 +4141,13 @@
         <v>175</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>161</v>
@@ -4176,13 +4167,13 @@
         <v>168</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>161</v>
@@ -4202,13 +4193,13 @@
         <v>150</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>161</v>
@@ -4228,13 +4219,13 @@
         <v>142</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>161</v>
@@ -4254,13 +4245,13 @@
         <v>142</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>161</v>
@@ -4280,13 +4271,13 @@
         <v>142</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>161</v>
@@ -4306,13 +4297,13 @@
         <v>145</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>128</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>161</v>
@@ -4332,13 +4323,13 @@
         <v>148</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>128</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>161</v>
@@ -4358,13 +4349,13 @@
         <v>150</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>161</v>
@@ -4384,13 +4375,13 @@
         <v>153</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>158</v>
@@ -4410,13 +4401,13 @@
         <v>155</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>158</v>
@@ -4436,13 +4427,13 @@
         <v>201</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>158</v>
@@ -4462,13 +4453,13 @@
         <v>185</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>158</v>
@@ -4488,13 +4479,13 @@
         <v>177</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>158</v>
@@ -4514,13 +4505,13 @@
         <v>168</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>158</v>
@@ -4540,13 +4531,13 @@
         <v>161</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>182</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>155</v>
@@ -4566,13 +4557,13 @@
         <v>153</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>172</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>155</v>
@@ -4592,13 +4583,13 @@
         <v>142</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>170</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>155</v>
@@ -4618,13 +4609,13 @@
         <v>139</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>334</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>155</v>
@@ -4644,13 +4635,13 @@
         <v>139</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>155</v>
@@ -4670,13 +4661,13 @@
         <v>139</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>155</v>
@@ -4696,13 +4687,13 @@
         <v>142</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>155</v>
@@ -4722,13 +4713,13 @@
         <v>155</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>158</v>
@@ -4748,13 +4739,13 @@
         <v>189</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>158</v>
@@ -4774,13 +4765,13 @@
         <v>185</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>161</v>
@@ -4800,13 +4791,13 @@
         <v>177</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>163</v>
@@ -4826,13 +4817,13 @@
         <v>168</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>163</v>
@@ -4852,13 +4843,13 @@
         <v>153</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>163</v>
@@ -4878,13 +4869,13 @@
         <v>142</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>163</v>
@@ -4904,13 +4895,13 @@
         <v>136</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>100</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>163</v>
@@ -4930,13 +4921,13 @@
         <v>133</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>165</v>
@@ -4956,13 +4947,13 @@
         <v>125</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>163</v>
@@ -4982,13 +4973,13 @@
         <v>120</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>163</v>
@@ -5008,13 +4999,13 @@
         <v>120</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>163</v>
@@ -5034,13 +5025,13 @@
         <v>125</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>163</v>
@@ -5060,13 +5051,13 @@
         <v>139</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>163</v>
@@ -5086,13 +5077,13 @@
         <v>219</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>163</v>
@@ -5112,13 +5103,13 @@
         <v>185</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>128</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>161</v>
@@ -5138,13 +5129,13 @@
         <v>179</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>155</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>158</v>
@@ -5164,13 +5155,13 @@
         <v>165</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>165</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>155</v>
@@ -5190,13 +5181,13 @@
         <v>161</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>175</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>155</v>
@@ -5216,13 +5207,13 @@
         <v>155</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F121" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G121" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>544</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>158</v>
@@ -5242,13 +5233,13 @@
         <v>158</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>429</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>158</v>
@@ -5268,13 +5259,13 @@
         <v>158</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>158</v>
@@ -5294,13 +5285,13 @@
         <v>158</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>158</v>
@@ -5320,13 +5311,13 @@
         <v>161</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>161</v>
@@ -5346,13 +5337,13 @@
         <v>172</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>161</v>
@@ -5372,13 +5363,13 @@
         <v>207</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>163</v>
@@ -5398,13 +5389,13 @@
         <v>221</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>161</v>
@@ -5424,13 +5415,13 @@
         <v>219</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>161</v>
@@ -5450,13 +5441,13 @@
         <v>198</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>161</v>
@@ -5476,13 +5467,13 @@
         <v>194</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>161</v>
@@ -5502,13 +5493,13 @@
         <v>170</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>161</v>
@@ -5528,13 +5519,13 @@
         <v>148</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>161</v>
@@ -5554,13 +5545,13 @@
         <v>136</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>161</v>
@@ -5580,13 +5571,13 @@
         <v>131</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>161</v>
@@ -5606,13 +5597,13 @@
         <v>139</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>161</v>
@@ -5632,13 +5623,13 @@
         <v>148</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>161</v>
@@ -5658,13 +5649,13 @@
         <v>148</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>158</v>
@@ -5684,13 +5675,13 @@
         <v>150</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>128</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>161</v>
@@ -5710,13 +5701,13 @@
         <v>161</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>158</v>
@@ -5736,13 +5727,13 @@
         <v>165</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>158</v>
@@ -5762,13 +5753,13 @@
         <v>163</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>155</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>155</v>
@@ -5788,13 +5779,13 @@
         <v>161</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>155</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>153</v>
@@ -5814,13 +5805,13 @@
         <v>155</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>172</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>153</v>
@@ -5840,13 +5831,13 @@
         <v>155</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>161</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>153</v>
@@ -5866,13 +5857,13 @@
         <v>155</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>153</v>
@@ -5892,13 +5883,13 @@
         <v>155</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>155</v>
@@ -5918,13 +5909,13 @@
         <v>153</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>163</v>
@@ -5944,13 +5935,13 @@
         <v>153</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>163</v>
@@ -5970,13 +5961,13 @@
         <v>153</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>172</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>163</v>
@@ -5996,13 +5987,13 @@
         <v>213</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>118</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>163</v>
@@ -6022,13 +6013,13 @@
         <v>207</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>163</v>
@@ -6048,13 +6039,13 @@
         <v>177</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>165</v>
@@ -6074,13 +6065,13 @@
         <v>155</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>163</v>
@@ -6100,13 +6091,13 @@
         <v>108</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>163</v>
@@ -6126,13 +6117,13 @@
         <v>87</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>161</v>
@@ -6152,13 +6143,13 @@
         <v>69</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>161</v>
@@ -6178,13 +6169,13 @@
         <v>58</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>120</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>158</v>
@@ -6204,13 +6195,13 @@
         <v>58</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>112</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>155</v>
@@ -6230,13 +6221,13 @@
         <v>61</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>153</v>
@@ -6256,13 +6247,13 @@
         <v>63</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>110</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>150</v>
@@ -6282,13 +6273,13 @@
         <v>61</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>150</v>
@@ -6308,13 +6299,13 @@
         <v>63</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>115</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>150</v>
@@ -6334,13 +6325,13 @@
         <v>72</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>131</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>150</v>
@@ -6360,13 +6351,13 @@
         <v>87</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>128</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>148</v>
@@ -6386,13 +6377,13 @@
         <v>84</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>148</v>
@@ -6412,13 +6403,13 @@
         <v>81</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>148</v>
@@ -6438,41 +6429,15 @@
         <v>84</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>155</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A169" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="H169" s="1" t="s">
         <v>148</v>
       </c>
     </row>
